--- a/bm/KEHO/ISO.BM-KEHO-19-02 Kế hoạch thời gian thi công máy.xlsx
+++ b/bm/KEHO/ISO.BM-KEHO-19-02 Kế hoạch thời gian thi công máy.xlsx
@@ -58,7 +58,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -80,11 +80,110 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -104,6 +203,16 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -493,74 +602,74 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>CÔNG TY QS TECHNOLOGY</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="B1" s="9" t="n"/>
+      <c r="C1" s="9" t="n"/>
+      <c r="D1" s="9" t="n"/>
+      <c r="E1" s="9" t="n"/>
+      <c r="F1" s="9" t="n"/>
+      <c r="G1" s="9" t="n"/>
+      <c r="H1" s="9" t="n"/>
+      <c r="I1" s="9" t="n"/>
+      <c r="J1" s="9" t="n"/>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>Mã số: ISO.BM-KEHO-19-02</t>
         </is>
       </c>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
+      <c r="N1" s="9" t="n"/>
+      <c r="O1" s="9" t="n"/>
+      <c r="P1" s="9" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="A2" s="9" t="n"/>
+      <c r="B2" s="9" t="n"/>
+      <c r="C2" s="9" t="n"/>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="9" t="n"/>
+      <c r="F2" s="9" t="n"/>
+      <c r="G2" s="9" t="n"/>
+      <c r="H2" s="9" t="n"/>
+      <c r="I2" s="9" t="n"/>
+      <c r="J2" s="9" t="n"/>
+      <c r="K2" s="9" t="n"/>
+      <c r="L2" s="9" t="n"/>
+      <c r="M2" s="11" t="inlineStr">
         <is>
           <t>Ngày ban hành: 15/06/2026</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
+      <c r="N2" s="9" t="n"/>
+      <c r="O2" s="9" t="n"/>
+      <c r="P2" s="9" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="9" t="n"/>
+      <c r="G3" s="9" t="n"/>
+      <c r="H3" s="9" t="n"/>
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="9" t="n"/>
+      <c r="K3" s="9" t="n"/>
+      <c r="L3" s="9" t="n"/>
+      <c r="M3" s="11" t="inlineStr">
         <is>
           <t>Lần ban hành: 01</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n"/>
+      <c r="N3" s="9" t="n"/>
+      <c r="O3" s="9" t="n"/>
+      <c r="P3" s="9" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -572,12 +681,12 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Tên máy/Dự án:  ________________________________</t>
+          <t>Tên máy/Dự án:  ................................</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Khách hàng:  ________________________________</t>
+          <t>Khách hàng:  ................................</t>
         </is>
       </c>
     </row>
@@ -881,13 +990,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="I3:P3"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="A1:L3"/>
     <mergeCell ref="A4:P4"/>
-    <mergeCell ref="I2:P2"/>
+    <mergeCell ref="M2:P2"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="I5:P5"/>
-    <mergeCell ref="A1:H3"/>
-    <mergeCell ref="I1:P1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9"/>
